--- a/addons/other/other.xlsx
+++ b/addons/other/other.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PortableApps\GitHubDesktopPortable-Kaddons\Data\kaddons.github.io\addons\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD5149C-8AE3-4193-8763-7EF13B0A0B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75EC7D4-BDC2-43C6-9F84-9BFE8DAFCAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42650763-0125-4CBD-B687-4938702E81BA}"/>
   </bookViews>
@@ -1012,41 +1012,41 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B2" t="str">
         <f>"files/" &amp; A2</f>
-        <v>files/smart.stable-30.56.zip</v>
+        <v>files/tvupdate504.tmb</v>
       </c>
       <c r="C2" s="1">
-        <v>45988</v>
+        <v>46137</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B3" t="str">
         <f>"files/" &amp; A3</f>
-        <v>files/tvQA_20251112-Universal.zip</v>
+        <v>files/smart.stable-30.56.zip</v>
       </c>
       <c r="C3" s="1">
-        <v>45973</v>
+        <v>45988</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" t="str">
         <f>"files/" &amp; A4</f>
-        <v>files/tvQA_20251112-onn4KPro.zip</v>
+        <v>files/tvQA_20251112-Universal.zip</v>
       </c>
       <c r="C4" s="1">
         <v>45973</v>
@@ -1057,26 +1057,26 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="2" t="str">
+        <v>26</v>
+      </c>
+      <c r="B5" t="str">
         <f>"files/" &amp; A5</f>
-        <v>files/projectivy-20251109-FireTV.plbackup</v>
+        <v>files/tvQA_20251112-onn4KPro.zip</v>
       </c>
       <c r="C5" s="1">
-        <v>45970</v>
+        <v>45973</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" t="str">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="str">
         <f>"files/" &amp; A6</f>
-        <v>files/tvQA_20251109-FireTV.zip</v>
+        <v>files/projectivy-20251109-FireTV.plbackup</v>
       </c>
       <c r="C6" s="1">
         <v>45970</v>
@@ -1087,13 +1087,14 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
+      </c>
+      <c r="B7" t="str">
+        <f>"files/" &amp; A7</f>
+        <v>files/tvQA_20251109-FireTV.zip</v>
       </c>
       <c r="C7" s="1">
-        <v>45927</v>
+        <v>45970</v>
       </c>
       <c r="D7" t="s">
         <v>18</v>
@@ -1101,14 +1102,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" t="str">
-        <f>"files/" &amp; A8</f>
-        <v>files/projectivy-20250926-onn4KPro.plbackup</v>
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C8" s="1">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -1116,17 +1116,17 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" t="str">
         <f>"files/" &amp; A9</f>
-        <v>files/tvupdate504.tmb</v>
+        <v>files/projectivy-20250926-onn4KPro.plbackup</v>
       </c>
       <c r="C9" s="1">
         <v>45926</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">

--- a/addons/other/other.xlsx
+++ b/addons/other/other.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PortableApps\GitHubDesktopPortable-Kaddons\Data\kaddons.github.io\addons\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75EC7D4-BDC2-43C6-9F84-9BFE8DAFCAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D4A2ED0-EEE1-4064-B447-D197A4AB76D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42650763-0125-4CBD-B687-4938702E81BA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>smart.stable-30.56.zip</t>
+  </si>
+  <si>
+    <t>adb_tools.zip</t>
   </si>
 </sst>
 </file>
@@ -988,7 +991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D9A25EF-1B7A-4619-AB7A-FD7FFA861628}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="31.7109375" customWidth="1"/>
@@ -1012,56 +1015,56 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B2" t="str">
-        <f>"files/" &amp; A2</f>
-        <v>files/tvupdate504.tmb</v>
+        <f t="shared" ref="B2:B8" si="0">"files/" &amp; A2</f>
+        <v>files/adb_tools.zip</v>
       </c>
       <c r="C2" s="1">
-        <v>46137</v>
+        <v>46147</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B3" t="str">
-        <f>"files/" &amp; A3</f>
-        <v>files/smart.stable-30.56.zip</v>
+        <f t="shared" si="0"/>
+        <v>files/tvupdate504.tmb</v>
       </c>
       <c r="C3" s="1">
-        <v>45988</v>
+        <v>46137</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B4" t="str">
-        <f>"files/" &amp; A4</f>
-        <v>files/tvQA_20251112-Universal.zip</v>
+        <f t="shared" si="0"/>
+        <v>files/smart.stable-30.56.zip</v>
       </c>
       <c r="C4" s="1">
-        <v>45973</v>
+        <v>45988</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" t="str">
-        <f>"files/" &amp; A5</f>
-        <v>files/tvQA_20251112-onn4KPro.zip</v>
+        <f t="shared" si="0"/>
+        <v>files/tvQA_20251112-Universal.zip</v>
       </c>
       <c r="C5" s="1">
         <v>45973</v>
@@ -1072,26 +1075,26 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="2" t="str">
-        <f>"files/" &amp; A6</f>
-        <v>files/projectivy-20251109-FireTV.plbackup</v>
+        <v>26</v>
+      </c>
+      <c r="B6" t="str">
+        <f t="shared" si="0"/>
+        <v>files/tvQA_20251112-onn4KPro.zip</v>
       </c>
       <c r="C6" s="1">
-        <v>45970</v>
+        <v>45973</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" t="str">
-        <f>"files/" &amp; A7</f>
-        <v>files/tvQA_20251109-FireTV.zip</v>
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>files/projectivy-20251109-FireTV.plbackup</v>
       </c>
       <c r="C7" s="1">
         <v>45970</v>
@@ -1102,13 +1105,14 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
+      </c>
+      <c r="B8" t="str">
+        <f t="shared" si="0"/>
+        <v>files/tvQA_20251109-FireTV.zip</v>
       </c>
       <c r="C8" s="1">
-        <v>45927</v>
+        <v>45970</v>
       </c>
       <c r="D8" t="s">
         <v>18</v>
@@ -1116,14 +1120,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="str">
-        <f>"files/" &amp; A9</f>
-        <v>files/projectivy-20250926-onn4KPro.plbackup</v>
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C9" s="1">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="s">
         <v>18</v>
@@ -1131,29 +1134,29 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="str">
-        <f>"files/" &amp; A10</f>
-        <v>files/tvupdate510.tmb</v>
+        <f t="shared" ref="B10:B24" si="1">"files/" &amp; A10</f>
+        <v>files/projectivy-20250926-onn4KPro.plbackup</v>
       </c>
       <c r="C10" s="1">
         <v>45926</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B11" t="str">
-        <f>"files/" &amp; A11</f>
-        <v>files/adbcmd.txt</v>
+        <f t="shared" si="1"/>
+        <v>files/tvupdate510.tmb</v>
       </c>
       <c r="C11" s="1">
-        <v>45915</v>
+        <v>45926</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
@@ -1161,14 +1164,14 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B12" t="str">
-        <f>"files/" &amp; A12</f>
-        <v>files/scrcpy64-3.3.1.zip</v>
+        <f t="shared" si="1"/>
+        <v>files/adbcmd.txt</v>
       </c>
       <c r="C12" s="1">
-        <v>45903</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="s">
         <v>12</v>
@@ -1176,26 +1179,26 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B13" t="str">
-        <f>"files/" &amp; A13</f>
-        <v>files/projectivy-20250731-SonyTV.plbackup</v>
+        <f t="shared" si="1"/>
+        <v>files/scrcpy64-3.3.1.zip</v>
       </c>
       <c r="C13" s="1">
-        <v>45869</v>
+        <v>45903</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" t="str">
-        <f>"files/" &amp; A14</f>
-        <v>files/sparkletv-20250731.bak</v>
+        <f t="shared" si="1"/>
+        <v>files/projectivy-20250731-SonyTV.plbackup</v>
       </c>
       <c r="C14" s="1">
         <v>45869</v>
@@ -1206,11 +1209,11 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" t="str">
-        <f>"files/" &amp; A15</f>
-        <v>files/tvQA-20250731-SonyTV.zip</v>
+        <f t="shared" si="1"/>
+        <v>files/sparkletv-20250731.bak</v>
       </c>
       <c r="C15" s="1">
         <v>45869</v>
@@ -1221,14 +1224,14 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="str">
-        <f>"files/" &amp; A16</f>
-        <v>files/adguard.jpg</v>
+        <f t="shared" si="1"/>
+        <v>files/tvQA-20250731-SonyTV.zip</v>
       </c>
       <c r="C16" s="1">
-        <v>45849</v>
+        <v>45869</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -1236,11 +1239,11 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="str">
-        <f>"files/" &amp; A17</f>
-        <v>files/flixvision.png</v>
+        <f t="shared" si="1"/>
+        <v>files/adguard.jpg</v>
       </c>
       <c r="C17" s="1">
         <v>45849</v>
@@ -1251,41 +1254,41 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B18" t="str">
-        <f>"files/" &amp; A18</f>
-        <v>files/tvupdate.tmb</v>
+        <f t="shared" si="1"/>
+        <v>files/flixvision.png</v>
       </c>
       <c r="C18" s="1">
-        <v>45839</v>
+        <v>45849</v>
       </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B19" t="str">
-        <f>"files/" &amp; A19</f>
-        <v>files/adbtools.zip</v>
+        <f t="shared" si="1"/>
+        <v>files/tvupdate.tmb</v>
       </c>
       <c r="C19" s="1">
-        <v>43718</v>
+        <v>45839</v>
       </c>
       <c r="D19" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" t="str">
-        <f>"files/" &amp; A20</f>
-        <v>files/screen.txt</v>
+        <f t="shared" si="1"/>
+        <v>files/adbtools.zip</v>
       </c>
       <c r="C20" s="1">
         <v>43718</v>
@@ -1296,11 +1299,11 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" t="str">
-        <f>"files/" &amp; A21</f>
-        <v>files/solidzip.zip</v>
+        <f t="shared" si="1"/>
+        <v>files/screen.txt</v>
       </c>
       <c r="C21" s="1">
         <v>43718</v>
@@ -1311,11 +1314,11 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" t="str">
-        <f>"files/" &amp; A22</f>
-        <v>files/solidzip4k.zip</v>
+        <f t="shared" si="1"/>
+        <v>files/solidzip.zip</v>
       </c>
       <c r="C22" s="1">
         <v>43718</v>
@@ -1326,11 +1329,11 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B23" t="str">
-        <f>"files/" &amp; A23</f>
-        <v>files/wp1920746-wallpaper.jpg</v>
+        <f t="shared" si="1"/>
+        <v>files/solidzip4k.zip</v>
       </c>
       <c r="C23" s="1">
         <v>43718</v>
@@ -1339,9 +1342,24 @@
         <v>4</v>
       </c>
     </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" t="str">
+        <f t="shared" si="1"/>
+        <v>files/wp1920746-wallpaper.jpg</v>
+      </c>
+      <c r="C24" s="1">
+        <v>43718</v>
+      </c>
+      <c r="D24" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D23">
-    <sortCondition descending="1" ref="C1:C23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D24">
+    <sortCondition descending="1" ref="C1:C24"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
